--- a/02_DIA_inicio_2026_analisis_assets/rbd_9586_liceo-araucania_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9586_liceo-araucania_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{21D6D1B8-9303-48E3-86A3-56DDD76ACF62}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35225A2D-A53A-4B8A-8AD4-53979ECB19EF}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A281448E-07A6-40FF-9736-E6E2EB98FA45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{590E1373-22E9-4580-A29A-499FA9984A01}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B325436-332C-4B41-B3C0-32D73441D96F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{20963DA1-5F52-4AEE-879E-4573B48A39A7}"/>
 </file>